--- a/Employee_Reports_wi48/Harikaran Seenithamby Q0591.xlsx
+++ b/Employee_Reports_wi48/Harikaran Seenithamby Q0591.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-139</v>
+        <v>-142</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1330,11 +1330,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1379,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
